--- a/قائمة الوحدات الخاصة بالفوج20252026/قائمة جهة نابل فوج قرمبالية المدينة وحدة مريم الاسطرلابي.xlsx
+++ b/قائمة الوحدات الخاصة بالفوج20252026/قائمة جهة نابل فوج قرمبالية المدينة وحدة مريم الاسطرلابي.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\wetransfer_scouts_2026-02-06_2056\Scouts\قائمة الوحدات الخاصة بالفوج20252026\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
@@ -19,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="29">
   <si>
     <t>المعرف</t>
   </si>
@@ -100,12 +95,18 @@
   </si>
   <si>
     <t xml:space="preserve">مرام </t>
+  </si>
+  <si>
+    <t>code_unite</t>
+  </si>
+  <si>
+    <t>JWLA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -478,9 +479,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>27</v>
+      </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -507,8 +511,8 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>28</v>
       </c>
       <c r="B2">
         <v>900010751</v>
@@ -536,8 +540,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>28</v>
       </c>
       <c r="B3">
         <v>900000000</v>
@@ -565,8 +569,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
+      <c r="A4" t="s">
+        <v>28</v>
       </c>
       <c r="B4">
         <v>900011701</v>
@@ -594,8 +598,8 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2</v>
+      <c r="A5" t="s">
+        <v>28</v>
       </c>
       <c r="B5">
         <v>900014629</v>
@@ -617,8 +621,8 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>3</v>
+      <c r="A6" t="s">
+        <v>28</v>
       </c>
       <c r="B6">
         <v>900011089</v>
@@ -643,8 +647,8 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>4</v>
+      <c r="A7" t="s">
+        <v>28</v>
       </c>
       <c r="B7">
         <v>900010026</v>
@@ -669,8 +673,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>5</v>
+      <c r="A8" t="s">
+        <v>28</v>
       </c>
       <c r="B8">
         <v>900007805</v>
@@ -695,8 +699,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>6</v>
+      <c r="A9" t="s">
+        <v>28</v>
       </c>
       <c r="B9">
         <v>900010253</v>
@@ -723,7 +727,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1 A2:F2 I2 A4:G4 I4" numberStoredAsText="1"/>
+    <ignoredError sqref="B1:I1 B2:F2 I2 B4:G4 I4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>